--- a/evaluation/gcmc/CALF_20/data.xlsx
+++ b/evaluation/gcmc/CALF_20/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GithubDesk\GTsR\evaluation\gcmc\CALF_20\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9724AE-A146-4086-8857-B97C03E2637E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED154939-A053-4416-8293-1243984840F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9405" yWindow="4118" windowWidth="13320" windowHeight="11917" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>name</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>logS</t>
+  </si>
+  <si>
+    <t>raspa2</t>
   </si>
 </sst>
 </file>
@@ -387,14 +390,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,16 +422,40 @@
       <c r="H1" t="s">
         <v>10</v>
       </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1">
-        <v>0.68112649999999997</v>
+        <v>4.3880860000000001E-2</v>
       </c>
       <c r="C2" s="1">
-        <v>2.061025E-2</v>
+        <v>1.1959620000000001E-3</v>
       </c>
       <c r="D2" s="1">
         <v>0.65588389999999996</v>
@@ -441,14 +468,37 @@
       </c>
       <c r="G2" s="1">
         <f>B2*0.9996/D2/0.0004</f>
-        <v>2595.1774750073914</v>
+        <v>167.1915854924934</v>
       </c>
       <c r="H2">
         <f>LOG10(G2)</f>
-        <v>3.4141670630634109</v>
+        <v>2.2232144162481164</v>
+      </c>
+      <c r="K2">
+        <v>4.6675981300000002E-2</v>
+      </c>
+      <c r="L2">
+        <v>1.2492568000000001E-3</v>
+      </c>
+      <c r="M2">
+        <v>0.63035318439999999</v>
+      </c>
+      <c r="N2">
+        <v>9.8208723000000001E-3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2">
+        <f>K2*0.9996/M2/0.0004</f>
+        <v>185.04432143025755</v>
+      </c>
+      <c r="Q2">
+        <f>LOG10(P2)</f>
+        <v>2.2672757621717721</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
